--- a/help/ORTHO-IMAGE.xlsx
+++ b/help/ORTHO-IMAGE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f81776d1a76517b/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkd6b\.lichtfeld\plugins\GIS_Tools\help\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{3F8062C9-E559-4B89-9233-7DA7AFB5E217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43341439-848A-4958-9BDD-784AAB908421}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D11885-9F56-4F1D-B1EA-04FFE3F70C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{BC766F53-F171-4675-8940-00028F7CD774}"/>
+    <workbookView xWindow="3456" yWindow="2868" windowWidth="18348" windowHeight="16332" xr2:uid="{BC766F53-F171-4675-8940-00028F7CD774}"/>
   </bookViews>
   <sheets>
     <sheet name="GIS-Tools" sheetId="1" r:id="rId1"/>
@@ -126,19 +126,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -349,14 +343,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -372,42 +363,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -456,13 +420,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>182640</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:colOff>228360</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>91020</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2811960" cy="38520"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="2" name="Ink 1">
@@ -476,12 +440,12 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="4327920" y="3253320"/>
+            <a:off x="2529600" y="4160100"/>
             <a:ext cx="2811960" cy="38520"/>
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="2" name="Ink 1">
@@ -516,13 +480,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>190200</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:colOff>144480</xdr:colOff>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>45360</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="83520" cy="106200"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="3" name="Ink 2">
@@ -536,12 +500,12 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="4335480" y="3200040"/>
+            <a:off x="2445720" y="4114440"/>
             <a:ext cx="83520" cy="106200"/>
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="3" name="Ink 2">
@@ -576,13 +540,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>167520</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>91260</xdr:rowOff>
+      <xdr:colOff>198000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114120</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2796840" cy="30600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Ink 3">
@@ -596,12 +560,12 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="4312800" y="3497400"/>
+            <a:off x="2499240" y="3931740"/>
             <a:ext cx="2796840" cy="30600"/>
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Ink 3">
@@ -636,13 +600,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>167520</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>41580</xdr:rowOff>
+      <xdr:colOff>68460</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>79680</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="185040" cy="143640"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
@@ -656,12 +620,12 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="4312800" y="3447720"/>
+            <a:off x="2369700" y="3897300"/>
             <a:ext cx="185040" cy="143640"/>
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -701,8 +665,8 @@
       <xdr:rowOff>77040</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3323160" cy="380160"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Ink 5">
@@ -721,7 +685,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Ink 5">
@@ -761,8 +725,8 @@
       <xdr:rowOff>175320</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3353400" cy="720"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="7" name="Ink 6">
@@ -781,7 +745,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="7" name="Ink 6">
@@ -821,8 +785,8 @@
       <xdr:rowOff>205560</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="252000" cy="389160"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="8" name="Ink 7">
@@ -841,7 +805,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="8" name="Ink 7">
@@ -881,8 +845,8 @@
       <xdr:rowOff>91080</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="435240" cy="720"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="9" name="Ink 8">
@@ -901,7 +865,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="9" name="Ink 8">
@@ -941,8 +905,8 @@
       <xdr:rowOff>205560</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="217800" cy="351360"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="10" name="Ink 9">
@@ -961,7 +925,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="10" name="Ink 9">
@@ -1001,8 +965,8 @@
       <xdr:rowOff>106200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1326240" cy="1646280"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="11" name="Ink 10">
@@ -1021,7 +985,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="11" name="Ink 10">
@@ -1061,8 +1025,8 @@
       <xdr:rowOff>52920</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1547280" cy="1744920"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="12" name="Ink 11">
@@ -1081,7 +1045,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="12" name="Ink 11">
@@ -1121,8 +1085,8 @@
       <xdr:rowOff>14940</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="720" cy="2202840"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="13" name="Ink 12">
@@ -1141,7 +1105,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="13" name="Ink 12">
@@ -1181,8 +1145,8 @@
       <xdr:rowOff>243360</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="252720" cy="250560"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="14" name="Ink 13">
@@ -1201,7 +1165,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="14" name="Ink 13">
@@ -1241,8 +1205,8 @@
       <xdr:rowOff>83520</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="142200" cy="239040"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="15" name="Ink 14">
@@ -1261,7 +1225,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="15" name="Ink 14">
@@ -1301,8 +1265,8 @@
       <xdr:rowOff>91080</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="114480" cy="213840"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="16" name="Ink 15">
@@ -1321,7 +1285,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="16" name="Ink 15">
@@ -1361,8 +1325,8 @@
       <xdr:rowOff>7200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3437280" cy="720"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="17" name="Ink 16">
@@ -1381,7 +1345,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="17" name="Ink 16">
@@ -1421,8 +1385,8 @@
       <xdr:rowOff>174960</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3467160" cy="8280"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId33">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="18" name="Ink 17">
@@ -1441,7 +1405,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="18" name="Ink 17">
@@ -1481,8 +1445,8 @@
       <xdr:rowOff>15060</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="720" cy="1036800"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId35">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="19" name="Ink 18">
@@ -1501,7 +1465,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="19" name="Ink 18">
@@ -1541,8 +1505,8 @@
       <xdr:rowOff>30240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="152640" cy="131400"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId37">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="20" name="Ink 19">
@@ -1561,7 +1525,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="20" name="Ink 19">
@@ -1601,8 +1565,8 @@
       <xdr:rowOff>251100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="106920" cy="175320"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId39">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="21" name="Ink 20">
@@ -1621,7 +1585,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="21" name="Ink 20">
@@ -1661,8 +1625,8 @@
       <xdr:rowOff>43920</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="89280" cy="146520"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId41">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="22" name="Ink 21">
@@ -1681,7 +1645,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="22" name="Ink 21">
@@ -1721,8 +1685,8 @@
       <xdr:rowOff>182520</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="221400" cy="373680"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId43">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="23" name="Ink 22">
@@ -1741,7 +1705,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="23" name="Ink 22">
@@ -1781,8 +1745,8 @@
       <xdr:rowOff>7200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="267120" cy="373680"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="24" name="Ink 23">
@@ -1801,7 +1765,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="24" name="Ink 23">
@@ -1841,8 +1805,8 @@
       <xdr:rowOff>7200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="426960" cy="15840"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId47">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="25" name="Ink 24">
@@ -1861,7 +1825,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="25" name="Ink 24">
@@ -1901,8 +1865,8 @@
       <xdr:rowOff>37980</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="360" cy="360"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId49">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="26" name="Ink 25">
@@ -1921,7 +1885,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="26" name="Ink 25">
@@ -1961,8 +1925,8 @@
       <xdr:rowOff>22680</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="594360" cy="708840"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId51">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="27" name="Ink 26">
@@ -1981,7 +1945,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="27" name="Ink 26">
@@ -2021,8 +1985,8 @@
       <xdr:rowOff>7200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="495720" cy="701640"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId53">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="28" name="Ink 27">
@@ -2041,7 +2005,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="28" name="Ink 27">
@@ -2081,8 +2045,8 @@
       <xdr:rowOff>121680</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7920" cy="191160"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink">
+      <mc:Choice Requires="xdr14 aink">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId55">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="29" name="Ink 28">
@@ -2101,7 +2065,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="29" name="Ink 28">
@@ -2141,8 +2105,8 @@
       <xdr:rowOff>98640</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7920" cy="214200"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink">
+      <mc:Choice Requires="xdr14 aink">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId57">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="30" name="Ink 29">
@@ -2161,7 +2125,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="30" name="Ink 29">
@@ -2201,8 +2165,8 @@
       <xdr:rowOff>114120</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="227880" cy="25200"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId59">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="31" name="Ink 30">
@@ -2221,7 +2185,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="31" name="Ink 30">
@@ -2261,8 +2225,8 @@
       <xdr:rowOff>28440</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="254880" cy="1129680"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId61">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="32" name="Ink 31">
@@ -2281,7 +2245,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="32" name="Ink 31">
@@ -2321,8 +2285,8 @@
       <xdr:rowOff>14760</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="41040" cy="11520"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId63">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="33" name="Ink 32">
@@ -2341,7 +2305,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="33" name="Ink 32">
@@ -2381,8 +2345,8 @@
       <xdr:rowOff>30240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="366120" cy="213480"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId65">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="34" name="Ink 33">
@@ -2401,7 +2365,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="34" name="Ink 33">
@@ -2441,8 +2405,8 @@
       <xdr:rowOff>151920</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="52560" cy="84600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId67">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="35" name="Ink 34">
@@ -2461,7 +2425,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="35" name="Ink 34">
@@ -2501,8 +2465,8 @@
       <xdr:rowOff>150840</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="104400" cy="123840"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId69">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="36" name="Ink 35">
@@ -2521,7 +2485,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="36" name="Ink 35">
@@ -2561,8 +2525,8 @@
       <xdr:rowOff>98640</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="654480" cy="99720"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId71">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="37" name="Ink 36">
@@ -2581,7 +2545,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="37" name="Ink 36">
@@ -2621,8 +2585,8 @@
       <xdr:rowOff>53100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="360" cy="360"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId73">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="38" name="Ink 37">
@@ -2641,7 +2605,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="38" name="Ink 37">
@@ -4009,7 +3973,7 @@
   <dimension ref="A3:S37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.77734375" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" customWidth="1"/>
     <col min="2" max="2" width="4.77734375" customWidth="1"/>
     <col min="3" max="14" width="3.77734375" customWidth="1"/>
     <col min="18" max="18" width="20.44140625" bestFit="1" customWidth="1"/>
@@ -4067,214 +4031,214 @@
     </row>
     <row r="7" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
     </row>
     <row r="8" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
     </row>
     <row r="9" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
     </row>
     <row r="10" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>4</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
     </row>
     <row r="11" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
     </row>
     <row r="12" spans="1:14" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>14</v>
       </c>
       <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
+        <v>7</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
     </row>
     <row r="13" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
+        <v>6</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
     </row>
     <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
     </row>
     <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15">
-        <v>9</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
     </row>
     <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16">
-        <v>10</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
     </row>
     <row r="17" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17">
-        <v>11</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
+        <v>2</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
     </row>
     <row r="18" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18">
-        <v>12</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
     </row>
     <row r="19" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4287,12 +4251,12 @@
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
+      <c r="A24" s="23"/>
       <c r="P24" t="s">
         <v>9</v>
       </c>
@@ -4330,7 +4294,7 @@
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="Q31" s="23">
+      <c r="Q31" s="22">
         <f>2 * DEGREES(ATAN(Q28 / (2 * Q29 * Q30)))</f>
         <v>6.9005627917824732</v>
       </c>
@@ -4395,14 +4359,14 @@
     <mergeCell ref="A23:A24"/>
   </mergeCells>
   <conditionalFormatting sqref="Q31">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>10</formula>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>6089</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>6.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <formula>6089</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
